--- a/outputs/technique_selection_history.xlsx
+++ b/outputs/technique_selection_history.xlsx
@@ -55,10 +55,10 @@
     <t>medium</t>
   </si>
   <si>
+    <t>long</t>
+  </si>
+  <si>
     <t>short</t>
-  </si>
-  <si>
-    <t>long</t>
   </si>
   <si>
     <t>Sep-2026</t>
@@ -486,13 +486,13 @@
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D3" t="s">
         <v>15</v>
@@ -504,7 +504,7 @@
         <v>18</v>
       </c>
       <c r="H3" s="2">
-        <v>46273.8889531713</v>
+        <v>46274.10382642361</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -515,19 +515,19 @@
         <v>11</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
         <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
       </c>
       <c r="H4" s="2">
-        <v>46274.10382642361</v>
+        <v>46274.10708666666</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -544,24 +544,24 @@
         <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s">
         <v>18</v>
       </c>
       <c r="H5" s="2">
-        <v>46274.10708666666</v>
+        <v>46274.10718293981</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" t="s">
         <v>15</v>
@@ -573,7 +573,7 @@
         <v>18</v>
       </c>
       <c r="H6" s="2">
-        <v>46274.10718294459</v>
+        <v>46274.97415523706</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/technique_selection_history.xlsx
+++ b/outputs/technique_selection_history.xlsx
@@ -40,16 +40,16 @@
     <t>Timestamp</t>
   </si>
   <si>
+    <t>wheat</t>
+  </si>
+  <si>
     <t>copper</t>
   </si>
   <si>
-    <t>wheat</t>
+    <t>North America</t>
   </si>
   <si>
     <t>Europe</t>
-  </si>
-  <si>
-    <t>North America</t>
   </si>
   <si>
     <t>medium</t>
@@ -481,53 +481,53 @@
         <v>18</v>
       </c>
       <c r="H2" s="2">
-        <v>46273.88797107639</v>
+        <v>46274.10382642361</v>
       </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="s">
         <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F3" t="s">
         <v>18</v>
       </c>
       <c r="H3" s="2">
-        <v>46274.10382642361</v>
+        <v>46274.10708666666</v>
       </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
         <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
         <v>18</v>
       </c>
       <c r="H4" s="2">
-        <v>46274.10708666666</v>
+        <v>46274.10718293981</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -538,7 +538,7 @@
         <v>11</v>
       </c>
       <c r="C5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D5" t="s">
         <v>15</v>
@@ -550,15 +550,15 @@
         <v>18</v>
       </c>
       <c r="H5" s="2">
-        <v>46274.10718293981</v>
+        <v>46275.56907113426</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" t="s">
         <v>14</v>
@@ -573,7 +573,7 @@
         <v>18</v>
       </c>
       <c r="H6" s="2">
-        <v>46274.97415523706</v>
+        <v>46275.57119427972</v>
       </c>
     </row>
   </sheetData>
